--- a/indexes/nc_build_all/clean_cat.xlsx
+++ b/indexes/nc_build_all/clean_cat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\maximilien\adresse\magisnc-dinum-api-adresses-f752eef9c72d\magisnc-dinum-api-adresses-f752eef9c72d\indexes\nc_build_all\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BAPA\projets\DINUM\2025_API_ADRESSE\code\magis-dinum-api-adresses\indexes\nc_build_all\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEC670D4-DA2E-4E9B-A9D9-F0BA14220E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FC51CA-705B-4822-A84F-CC9C4A25699F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="18420" yWindow="2835" windowWidth="21600" windowHeight="11385" xr2:uid="{DDE60798-8F18-41CD-9232-3F88E1F48177}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DDE60798-8F18-41CD-9232-3F88E1F48177}"/>
   </bookViews>
   <sheets>
     <sheet name="clean_cat" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -38,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
-    <t>category</t>
-  </si>
-  <si>
     <t>complet_cat</t>
   </si>
   <si>
@@ -101,9 +101,6 @@
     <t>PARC</t>
   </si>
   <si>
-    <t>PARC ESPACE PUBLIC ET LOISIR</t>
-  </si>
-  <si>
     <t>SCIVILE</t>
   </si>
   <si>
@@ -132,6 +129,12 @@
   </si>
   <si>
     <t>TRANSPORT</t>
+  </si>
+  <si>
+    <t>PARC ESPACE PUBLIC</t>
+  </si>
+  <si>
+    <t>PARC ESPACE PUBLIC ET LOISIR</t>
   </si>
 </sst>
 </file>
@@ -508,146 +511,146 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
         <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/indexes/nc_build_all/clean_cat.xlsx
+++ b/indexes/nc_build_all/clean_cat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BAPA\projets\DINUM\2025_API_ADRESSE\code\magis-dinum-api-adresses\indexes\nc_build_all\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\maximilien\adresse\magisnc-dinum-api-adresses-f752eef9c72d\magisnc-dinum-api-adresses-f752eef9c72d\indexes\nc_build_all\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FC51CA-705B-4822-A84F-CC9C4A25699F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEC670D4-DA2E-4E9B-A9D9-F0BA14220E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DDE60798-8F18-41CD-9232-3F88E1F48177}"/>
+    <workbookView minimized="1" xWindow="18420" yWindow="2835" windowWidth="21600" windowHeight="11385" xr2:uid="{DDE60798-8F18-41CD-9232-3F88E1F48177}"/>
   </bookViews>
   <sheets>
     <sheet name="clean_cat" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -41,6 +38,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
+    <t>category</t>
+  </si>
+  <si>
     <t>complet_cat</t>
   </si>
   <si>
@@ -101,6 +101,9 @@
     <t>PARC</t>
   </si>
   <si>
+    <t>PARC ESPACE PUBLIC ET LOISIR</t>
+  </si>
+  <si>
     <t>SCIVILE</t>
   </si>
   <si>
@@ -129,12 +132,6 @@
   </si>
   <si>
     <t>TRANSPORT</t>
-  </si>
-  <si>
-    <t>PARC ESPACE PUBLIC</t>
-  </si>
-  <si>
-    <t>PARC ESPACE PUBLIC ET LOISIR</t>
   </si>
 </sst>
 </file>
@@ -511,146 +508,146 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/indexes/nc_build_all/clean_cat.xlsx
+++ b/indexes/nc_build_all/clean_cat.xlsx
@@ -1,155 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\maximilien\adresse\magisnc-dinum-api-adresses-f752eef9c72d\magisnc-dinum-api-adresses-f752eef9c72d\indexes\nc_build_all\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEC670D4-DA2E-4E9B-A9D9-F0BA14220E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="18420" yWindow="2835" windowWidth="21600" windowHeight="11385" xr2:uid="{DDE60798-8F18-41CD-9232-3F88E1F48177}"/>
+    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18420" yWindow="2835" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="clean_cat" sheetId="1" r:id="rId1"/>
+    <sheet name="clean_cat" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>complet_cat</t>
-  </si>
-  <si>
-    <t>ADMIN</t>
-  </si>
-  <si>
-    <t>ADMINISTRATION ET ORGANISME</t>
-  </si>
-  <si>
-    <t>ADRESSE</t>
-  </si>
-  <si>
-    <t>AGRIC</t>
-  </si>
-  <si>
-    <t>AGRICOLE ET COMMERCIAL</t>
-  </si>
-  <si>
-    <t>CADASTRE</t>
-  </si>
-  <si>
-    <t>CULT</t>
-  </si>
-  <si>
-    <t>CULTUREL ET SOCIO EDUCATIF</t>
-  </si>
-  <si>
-    <t>DECHET</t>
-  </si>
-  <si>
-    <t>DECHETS</t>
-  </si>
-  <si>
-    <t>ENSEIG</t>
-  </si>
-  <si>
-    <t>ENSEIGNEMENT ET FORMATION</t>
-  </si>
-  <si>
-    <t>ENERGIE</t>
-  </si>
-  <si>
-    <t>ENERGIE ET INDUSTRIE</t>
-  </si>
-  <si>
-    <t>EQ_SPORT</t>
-  </si>
-  <si>
-    <t>EQUIPEMENT SPORTIF</t>
-  </si>
-  <si>
-    <t>LOCAL</t>
-  </si>
-  <si>
-    <t>LOCALISATION</t>
-  </si>
-  <si>
-    <t>PARC</t>
-  </si>
-  <si>
-    <t>PARC ESPACE PUBLIC ET LOISIR</t>
-  </si>
-  <si>
-    <t>SCIVILE</t>
-  </si>
-  <si>
-    <t>SECURITE CIVILE</t>
-  </si>
-  <si>
-    <t>RELIGIEUX</t>
-  </si>
-  <si>
-    <t>SANIT</t>
-  </si>
-  <si>
-    <t>SANITAIRE ET SOCIAL</t>
-  </si>
-  <si>
-    <t>SITE</t>
-  </si>
-  <si>
-    <t>SITE NATUREL</t>
-  </si>
-  <si>
-    <t>TOURISME</t>
-  </si>
-  <si>
-    <t>TRANSP</t>
-  </si>
-  <si>
-    <t>TRANSPORT</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -168,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -502,161 +439,231 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE6D69C-2F42-4942-8B51-2F539FAD3634}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>complet_cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION ET ORGANISME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADRESSE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADRESSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AGRIC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AGRICOLE ET COMMERCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CADASTRE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CADASTRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CULT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CULTUREL ET SOCIO EDUCATIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DECHET</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DECHETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ENSEIG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ENSEIGNEMENT ET FORMATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ENERGIE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ENERGIE ET INDUSTRIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EQ_SPORT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EQUIPEMENT SPORTIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LOCAL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LOCALISATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PARC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PARC ESPACE PUBLIC ET LOISIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCIVILE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SECURITE CIVILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RELIGIEUX</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RELIGIEUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SANIT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SANITAIRE ET SOCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SITE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SITE NATUREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TOURISME</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TOURISME</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TRANSP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TRANSPORT</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{c135c4ba-2280-41f8-be7d-6f21d368baa3}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>